--- a/output_data/charts/crashSeverityByType-Marion.xlsx
+++ b/output_data/charts/crashSeverityByType-Marion.xlsx
@@ -34,46 +34,46 @@
     <t>Angle</t>
   </si>
   <si>
+    <t>Sideswipe - Passing</t>
+  </si>
+  <si>
     <t>Left Turn</t>
   </si>
   <si>
     <t>Pedestrian</t>
   </si>
   <si>
+    <t>Animal</t>
+  </si>
+  <si>
     <t>Head On</t>
   </si>
   <si>
     <t>Other Non-Collision</t>
   </si>
   <si>
-    <t>Animal</t>
-  </si>
-  <si>
     <t>Parked Vehicle</t>
   </si>
   <si>
-    <t>Sideswipe - Passing</t>
-  </si>
-  <si>
     <t>Overturning</t>
   </si>
   <si>
+    <t>Pedalcycles</t>
+  </si>
+  <si>
     <t>Other Object</t>
   </si>
   <si>
+    <t>Rear End</t>
+  </si>
+  <si>
+    <t>Right Turn</t>
+  </si>
+  <si>
+    <t>Sideswipe - Meeting</t>
+  </si>
+  <si>
     <t>Backing</t>
-  </si>
-  <si>
-    <t>Rear End</t>
-  </si>
-  <si>
-    <t>Pedalcycles</t>
-  </si>
-  <si>
-    <t>Right Turn</t>
-  </si>
-  <si>
-    <t>Sideswipe - Meeting</t>
   </si>
   <si>
     <t>Train</t>
@@ -222,46 +222,46 @@
                   <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Left Turn</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Head On</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>Pedalcycles</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Rear End</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Pedalcycles</c:v>
+                  <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Right Turn</c:v>
+                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Sideswipe - Meeting</c:v>
+                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Train</c:v>
@@ -279,28 +279,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>42.22222222222222</c:v>
+                  <c:v>35.55555555555556</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>28.88888888888889</c:v>
+                  <c:v>24.44444444444444</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>8.888888888888889</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>6.666666666666667</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>4.444444444444445</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>4.444444444444445</c:v>
+                  <c:v>6.666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>4.444444444444445</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2.222222222222222</c:v>
+                  <c:v>4.444444444444445</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>2.222222222222222</c:v>
+                  <c:v>4.444444444444445</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>2.222222222222222</c:v>
@@ -370,46 +370,46 @@
                   <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Left Turn</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Head On</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>Pedalcycles</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Rear End</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Pedalcycles</c:v>
+                  <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Right Turn</c:v>
+                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Sideswipe - Meeting</c:v>
+                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Train</c:v>
@@ -427,46 +427,46 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>27.17391304347826</c:v>
+                  <c:v>28.27225130890053</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>26.6304347826087</c:v>
+                  <c:v>23.56020942408377</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9.239130434782608</c:v>
+                  <c:v>7.329842931937172</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6.521739130434782</c:v>
+                  <c:v>7.853403141361256</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.608695652173914</c:v>
+                  <c:v>8.37696335078534</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.08695652173913</c:v>
+                  <c:v>1.047120418848168</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.630434782608696</c:v>
+                  <c:v>6.282722513089005</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.630434782608696</c:v>
+                  <c:v>3.141361256544502</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>6.521739130434782</c:v>
+                  <c:v>0.5235602094240838</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.717391304347826</c:v>
+                  <c:v>3.141361256544502</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0</c:v>
+                  <c:v>5.235602094240837</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>4.891304347826087</c:v>
+                  <c:v>4.712041884816754</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>4.347826086956522</c:v>
+                  <c:v>0.5235602094240838</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>0</c:v>
@@ -518,46 +518,46 @@
                   <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>Left Turn</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="4">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Head On</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="7">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="10">
+                  <c:v>Pedalcycles</c:v>
+                </c:pt>
+                <c:pt idx="11">
                   <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>Rear End</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>Pedalcycles</c:v>
+                  <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>Right Turn</c:v>
+                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>Sideswipe - Meeting</c:v>
+                  <c:v>Backing</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>Train</c:v>
@@ -575,58 +575,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="18"/>
                 <c:pt idx="0">
-                  <c:v>17.20086834376197</c:v>
+                  <c:v>16.58511460211177</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15.09385774486017</c:v>
+                  <c:v>15.07854751480814</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.133444004597114</c:v>
+                  <c:v>11.18980169971671</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.7151066275060657</c:v>
+                  <c:v>5.53695596188514</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.532371344655855</c:v>
+                  <c:v>0.6824620139067731</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2.145319882518197</c:v>
+                  <c:v>16.03141900592325</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>15.74511556633891</c:v>
+                  <c:v>1.532320370847283</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>4.737581407227685</c:v>
+                  <c:v>2.382178727787793</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10.9053760694675</c:v>
+                  <c:v>4.906000515065671</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.6895671050951347</c:v>
+                  <c:v>0.6695853721349472</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.6767973438896693</c:v>
+                  <c:v>0.6824620139067731</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>4.788660452049546</c:v>
+                  <c:v>0.6824620139067731</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>16.72838717915975</c:v>
+                  <c:v>15.76100952871491</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.6001787766568765</c:v>
+                  <c:v>2.369302086015967</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.413484867832972</c:v>
+                  <c:v>0.01287664177182591</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01276976120546546</c:v>
+                  <c:v>5.047643574555756</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.07661856723279274</c:v>
+                  <c:v>0.09013649240278136</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.804494955944324</c:v>
+                  <c:v>0.7597218645377286</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1082,13 +1082,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>42.22222222222222</v>
+        <v>35.55555555555556</v>
       </c>
       <c r="C2" s="2">
-        <v>27.17391304347826</v>
+        <v>28.27225130890053</v>
       </c>
       <c r="D2" s="2">
-        <v>17.20086834376197</v>
+        <v>16.58511460211177</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1096,13 +1096,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>28.88888888888889</v>
+        <v>24.44444444444444</v>
       </c>
       <c r="C3" s="2">
-        <v>26.6304347826087</v>
+        <v>23.56020942408377</v>
       </c>
       <c r="D3" s="2">
-        <v>15.09385774486017</v>
+        <v>15.07854751480814</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1110,13 +1110,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>6.666666666666667</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="C4" s="2">
-        <v>9.239130434782608</v>
+        <v>7.329842931937172</v>
       </c>
       <c r="D4" s="2">
-        <v>5.133444004597114</v>
+        <v>11.18980169971671</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1124,13 +1124,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>4.444444444444445</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="C5" s="2">
-        <v>6.521739130434782</v>
+        <v>7.853403141361256</v>
       </c>
       <c r="D5" s="2">
-        <v>0.7151066275060657</v>
+        <v>5.53695596188514</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1138,13 +1138,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>4.444444444444445</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="C6" s="2">
-        <v>7.608695652173914</v>
+        <v>8.37696335078534</v>
       </c>
       <c r="D6" s="2">
-        <v>1.532371344655855</v>
+        <v>0.6824620139067731</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1155,10 +1155,10 @@
         <v>4.444444444444445</v>
       </c>
       <c r="C7" s="2">
-        <v>1.08695652173913</v>
+        <v>1.047120418848168</v>
       </c>
       <c r="D7" s="2">
-        <v>2.145319882518197</v>
+        <v>16.03141900592325</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1166,13 +1166,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>2.222222222222222</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="C8" s="2">
-        <v>1.630434782608696</v>
+        <v>6.282722513089005</v>
       </c>
       <c r="D8" s="2">
-        <v>15.74511556633891</v>
+        <v>1.532320370847283</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1180,13 +1180,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>2.222222222222222</v>
+        <v>4.444444444444445</v>
       </c>
       <c r="C9" s="2">
-        <v>1.630434782608696</v>
+        <v>3.141361256544502</v>
       </c>
       <c r="D9" s="2">
-        <v>4.737581407227685</v>
+        <v>2.382178727787793</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1197,10 +1197,10 @@
         <v>2.222222222222222</v>
       </c>
       <c r="C10" s="2">
-        <v>6.521739130434782</v>
+        <v>0.5235602094240838</v>
       </c>
       <c r="D10" s="2">
-        <v>10.9053760694675</v>
+        <v>4.906000515065671</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1211,10 +1211,10 @@
         <v>2.222222222222222</v>
       </c>
       <c r="C11" s="2">
-        <v>2.717391304347826</v>
+        <v>3.141361256544502</v>
       </c>
       <c r="D11" s="2">
-        <v>0.6895671050951347</v>
+        <v>0.6695853721349472</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1225,10 +1225,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>5.235602094240837</v>
       </c>
       <c r="D12" s="2">
-        <v>0.6767973438896693</v>
+        <v>0.6824620139067731</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="2">
-        <v>4.788660452049546</v>
+        <v>0.6824620139067731</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1253,10 +1253,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <v>4.891304347826087</v>
+        <v>4.712041884816754</v>
       </c>
       <c r="D14" s="2">
-        <v>16.72838717915975</v>
+        <v>15.76100952871491</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1267,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>4.347826086956522</v>
+        <v>0.5235602094240838</v>
       </c>
       <c r="D15" s="2">
-        <v>0.6001787766568765</v>
+        <v>2.369302086015967</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1284,7 +1284,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="2">
-        <v>2.413484867832972</v>
+        <v>0.01287664177182591</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1298,7 +1298,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>0.01276976120546546</v>
+        <v>5.047643574555756</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1312,7 +1312,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>0.07661856723279274</v>
+        <v>0.09013649240278136</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1326,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="2">
-        <v>0.804494955944324</v>
+        <v>0.7597218645377286</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Marion.xlsx
+++ b/output_data/charts/crashSeverityByType-Marion.xlsx
@@ -86,8 +86,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -144,7 +145,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -176,7 +177,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - Marion County</a:t>
+              <a:t>Crash Severity by Type of Crash, Marion County, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
